--- a/erp-server/erp-server-file/src/main/resources/excel/oms/InvoiceInfo.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/InvoiceInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="发票" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>发票号</t>
   </si>
@@ -71,6 +71,9 @@
     <t>文件路径</t>
   </si>
   <si>
+    <t>序列号/序号</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -111,6 +114,9 @@
   </si>
   <si>
     <t>{.fileUrl}</t>
+  </si>
+  <si>
+    <t>{.startCodeStr}</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.625" customWidth="1"/>
@@ -1106,9 +1112,10 @@
     <col min="10" max="10" width="18.25" customWidth="1"/>
     <col min="11" max="11" width="16.625" customWidth="1"/>
     <col min="12" max="12" width="14.25" customWidth="1"/>
+    <col min="15" max="15" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1151,49 +1158,55 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/InvoiceInfo.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/InvoiceInfo.xlsx
@@ -50,6 +50,9 @@
     <t>发票状态</t>
   </si>
   <si>
+    <t>序列号/序号</t>
+  </si>
+  <si>
     <t>生成时间</t>
   </si>
   <si>
@@ -71,9 +74,6 @@
     <t>文件路径</t>
   </si>
   <si>
-    <t>序列号/序号</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -95,6 +95,9 @@
     <t>{.statusName}</t>
   </si>
   <si>
+    <t>{.startCodeStr}</t>
+  </si>
+  <si>
     <t>{.billCreateTime}</t>
   </si>
   <si>
@@ -114,9 +117,6 @@
   </si>
   <si>
     <t>{.fileUrl}</t>
-  </si>
-  <si>
-    <t>{.startCodeStr}</t>
   </si>
 </sst>
 </file>
@@ -1107,12 +1107,12 @@
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="16.25" customWidth="1"/>
     <col min="7" max="7" width="16.625" customWidth="1"/>
-    <col min="8" max="8" width="22.25" customWidth="1"/>
-    <col min="9" max="9" width="17.25" customWidth="1"/>
-    <col min="10" max="10" width="18.25" customWidth="1"/>
-    <col min="11" max="11" width="16.625" customWidth="1"/>
-    <col min="12" max="12" width="14.25" customWidth="1"/>
-    <col min="15" max="15" width="13.625" customWidth="1"/>
+    <col min="8" max="9" width="22.25" customWidth="1"/>
+    <col min="10" max="10" width="17.25" customWidth="1"/>
+    <col min="11" max="11" width="18.25" customWidth="1"/>
+    <col min="12" max="12" width="16.625" customWidth="1"/>
+    <col min="13" max="13" width="14.25" customWidth="1"/>
+    <col min="16" max="16" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1137,7 +1137,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1152,7 +1152,7 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/InvoiceInfo.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/InvoiceInfo.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>开票公司</t>
+  </si>
+  <si>
+    <t>卖家税号</t>
+  </si>
   <si>
     <t>发票号</t>
   </si>
@@ -72,6 +78,12 @@
   </si>
   <si>
     <t>文件路径</t>
+  </si>
+  <si>
+    <t>{.companyName}</t>
+  </si>
+  <si>
+    <t>{.sellerTaxNo}</t>
   </si>
   <si>
     <t>{.code}</t>
@@ -768,9 +780,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1097,116 +1112,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="27.625" customWidth="1"/>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
-    <col min="3" max="3" width="19.875" customWidth="1"/>
-    <col min="4" max="4" width="15.75" customWidth="1"/>
-    <col min="5" max="5" width="15.625" customWidth="1"/>
-    <col min="6" max="6" width="16.25" customWidth="1"/>
-    <col min="7" max="7" width="16.625" customWidth="1"/>
-    <col min="8" max="9" width="22.25" customWidth="1"/>
-    <col min="10" max="10" width="17.25" customWidth="1"/>
-    <col min="11" max="11" width="18.25" customWidth="1"/>
-    <col min="12" max="12" width="16.625" customWidth="1"/>
-    <col min="13" max="13" width="14.25" customWidth="1"/>
-    <col min="16" max="16" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="35.25" customWidth="1"/>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="3" max="3" width="27.625" customWidth="1"/>
+    <col min="4" max="4" width="26.875" customWidth="1"/>
+    <col min="5" max="5" width="19.875" customWidth="1"/>
+    <col min="6" max="6" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="16.25" customWidth="1"/>
+    <col min="9" max="9" width="16.625" customWidth="1"/>
+    <col min="10" max="11" width="22.25" customWidth="1"/>
+    <col min="12" max="12" width="17.25" customWidth="1"/>
+    <col min="13" max="13" width="18.25" customWidth="1"/>
+    <col min="14" max="14" width="16.625" customWidth="1"/>
+    <col min="15" max="15" width="14.25" customWidth="1"/>
+    <col min="18" max="18" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="1:17">
+      <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>29</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
